--- a/DOSSIES_MULTIFORMATO/ADS/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/ADS/dossie.xlsx
@@ -632,12 +632,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024NE0001402</t>
+          <t>2024NE0001369</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2067.62</v>
+        <v>182.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,19 +655,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024NE0001369</t>
+          <t>2024NE0001402</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>182.45</v>
+        <v>2067.62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -685,19 +685,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023NE0001481</t>
+          <t>2023NE0001480</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10473.68</v>
+        <v>356.18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -715,19 +715,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 425/20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023NE0001480</t>
+          <t>2023NE0001481</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>356.18</v>
+        <v>10473.68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -745,19 +745,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 425/20</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2022NE0001461</t>
+          <t>2022NE0001467</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2618.42</v>
+        <v>1283.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -775,19 +775,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>reforço da NE 1182/22</t>
+          <t>reforço da NE 52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022NE0001467</t>
+          <t>2022NE0001461</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1283.8</v>
+        <v>2618.42</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>reforço da NE 52</t>
+          <t>reforço da NE 1182/22</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025NE0000775</t>
+          <t>2025NE0000773</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8270.48</v>
+        <v>10860.16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025NE0000773</t>
+          <t>2025NE0000775</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10860.16</v>
+        <v>8270.48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2015NE00257</t>
+          <t>2015NE00254</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>102/2012</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>1348.53</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>REFERENTE ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2015NE00034, EM VIRTUDE DA ALTERAÇÃO DA UNIDADE GESTORA.</t>
+          <t>REFERENTE ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2015NE00053, EM VIRTUDE DA ALTERAÇÃO DA UNIDADE GESTORA.</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2015NE00254</t>
+          <t>2015NE00257</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>102/2012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1348.53</v>
+        <v>0.04</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>REFERENTE ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2015NE00053, EM VIRTUDE DA ALTERAÇÃO DA UNIDADE GESTORA.</t>
+          <t>REFERENTE ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº 2015NE00034, EM VIRTUDE DA ALTERAÇÃO DA UNIDADE GESTORA.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2015NE00021</t>
+          <t>2015NE00015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>274/2010</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3943.41</v>
+        <v>2525.44</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1131,19 +1131,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4º (QUARTO) TERMO ADITIVO AO CONTRATO Nº 274/2010. OBJETO: PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP, CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL. OBJETIVO: PRORROGAR POR MAIS 12 (DOZE) MESE</t>
+          <t>1º (PRIMEIRO) TERMO ADITIVO AO CONTRATO Nº 428/2013. OBJETO: PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). OBJETIVO: PRORROGAR POR MAIS DOZE MESES, COM READEQUAÇÃO FINANCEIRA.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2015NE00015</t>
+          <t>2015NE00021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>274/2010</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2525.44</v>
+        <v>3943.41</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1161,19 +1161,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1º (PRIMEIRO) TERMO ADITIVO AO CONTRATO Nº 428/2013. OBJETO: PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). OBJETIVO: PRORROGAR POR MAIS DOZE MESES, COM READEQUAÇÃO FINANCEIRA.</t>
+          <t>4º (QUARTO) TERMO ADITIVO AO CONTRATO Nº 274/2010. OBJETO: PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP, CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL. OBJETIVO: PRORROGAR POR MAIS 12 (DOZE) MESE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2018NE00025</t>
+          <t>2018NE00024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16228.19</v>
+        <v>12862.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1191,19 +1191,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEOS E IMAGENS VIA WEBSITE.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE ACESSO GERENCIADO À REDE MUNDIAL, VIA REDE DE GOVERNO, ESTABELECENDO COMUNICAÇÃO A PARTIR DE CIRCUITO DE DADOS.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2018NE00024</t>
+          <t>2018NE00025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12862.8</v>
+        <v>16228.19</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1221,14 +1221,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE ACESSO GERENCIADO À REDE MUNDIAL, VIA REDE DE GOVERNO, ESTABELECENDO COMUNICAÇÃO A PARTIR DE CIRCUITO DE DADOS.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEOS E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2018NE01589</t>
+          <t>2018NE01588</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1475.29</v>
+        <v>2086</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2018NE01436</t>
+          <t>2018NE01590</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>165.22</v>
+        <v>2711.28</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anulação orçamentária de saldo, referente ao encerramento do exercício financeiro de 2018.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018NE01590</t>
+          <t>2018NE01436</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2711.28</v>
+        <v>165.22</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>Anulação orçamentária de saldo, referente ao encerramento do exercício financeiro de 2018.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE01588</t>
+          <t>2018NE01589</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2086</v>
+        <v>1475.29</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017NE01412</t>
+          <t>2017NE01402</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>825.42</v>
+        <v>1150.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017NE01403</t>
+          <t>2017NE01395</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>641.4400000000001</v>
+        <v>1150.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2017NE01400</t>
+          <t>2017NE01408</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1475.29</v>
+        <v>3312.24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2017NE01408</t>
+          <t>2017NE01400</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3312.24</v>
+        <v>1475.29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2017NE01395</t>
+          <t>2017NE01403</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1150.6</v>
+        <v>641.4400000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2017NE01402</t>
+          <t>2017NE01412</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1150.6</v>
+        <v>825.42</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025NE0001217</t>
+          <t>2025NE0001218</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2852.42</v>
+        <v>195.26</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1541,19 +1541,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025NE0001218</t>
+          <t>2025NE0001217</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>195.26</v>
+        <v>2852.42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2019NE01638</t>
+          <t>2019NE01640</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.02</v>
+        <v>5680.37</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2019NE01640</t>
+          <t>2019NE01638</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5680.37</v>
+        <v>0.02</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2022NE0001892</t>
+          <t>2022NE0001893</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24.12</v>
+        <v>2871.35</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2022NE0001893</t>
+          <t>2022NE0001892</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2871.35</v>
+        <v>24.12</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2022NE0001579</t>
+          <t>2022NE0001577</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1994.54</v>
+        <v>2618.42</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 1528</t>
+          <t>REFORÇO DA NE 1182</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2022NE0001577</t>
+          <t>2022NE0001579</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2618.42</v>
+        <v>1994.54</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1959,19 +1959,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 1182</t>
+          <t>REFORÇO DA NE 1528</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2023NE0001441</t>
+          <t>2023NE0001440</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>356.18</v>
+        <v>3983.08</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1989,19 +1989,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2023NE0001440</t>
+          <t>2023NE0001441</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3983.08</v>
+        <v>356.18</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2019,14 +2019,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2015NE00934</t>
+          <t>2015NE00935</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>277.89</v>
+        <v>417.75</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2015NE00935</t>
+          <t>2015NE00934</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>417.75</v>
+        <v>277.89</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2078,12 +2078,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2017NE01186</t>
+          <t>2017NE01187</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1121.5</v>
+        <v>449.51</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2101,19 +2101,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER OS CADASTROS DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA E CONTABILIDADE GERENCIAL CTBG.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2017NE01187</t>
+          <t>2017NE01186</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>449.51</v>
+        <v>1121.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA E CONTABILIDADE GERENCIAL CTBG.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER OS CADASTROS DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2016NE00721</t>
+          <t>2016NE00722</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>899.02</v>
+        <v>2243</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2161,19 +2161,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>À CONTRATAR OBJETO: LICENÇA DE USO DO SISTEMA CTBG - SISTEMA DE CONTABILIDADE GERENCIAL OBJETIVO: PROPORCIONAR A ADS A UTILIZAÇÃO DO SISTEMA DE CONTABILIDADE GERENCIAL, PARA EFETUAR SEUS LANÇAMENTOS C</t>
+          <t>À CONTRATAR OBJETO: PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH. OBJETIVO: MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE PAGAMENTO.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2016NE00722</t>
+          <t>2016NE00721</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2243</v>
+        <v>899.02</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2191,19 +2191,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>À CONTRATAR OBJETO: PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH. OBJETIVO: MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE PAGAMENTO.</t>
+          <t>À CONTRATAR OBJETO: LICENÇA DE USO DO SISTEMA CTBG - SISTEMA DE CONTABILIDADE GERENCIAL OBJETIVO: PROPORCIONAR A ADS A UTILIZAÇÃO DO SISTEMA DE CONTABILIDADE GERENCIAL, PARA EFETUAR SEUS LANÇAMENTOS C</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024NE0000480</t>
+          <t>2024NE0000478</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1991.54</v>
+        <v>178.09</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024NE0000478</t>
+          <t>2024NE0000480</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>178.09</v>
+        <v>1991.54</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2281,19 +2281,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2019NE00168</t>
+          <t>2019NE00175</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4903.86</v>
+        <v>1484.04</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2311,19 +2311,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteúdo web.</t>
+          <t>SERVIÇO DE LICENÇA DO SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2019NE00176</t>
+          <t>2019NE00166</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5313.15</v>
+        <v>19290.96</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS</t>
+          <t>Serviço de acesso gerencial a rede mundial via rede de governo (link de internet).</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2019NE00166</t>
+          <t>2019NE00176</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>19290.96</v>
+        <v>5313.15</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2401,19 +2401,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Serviço de acesso gerencial a rede mundial via rede de governo (link de internet).</t>
+          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2019NE00175</t>
+          <t>2019NE00168</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1484.04</v>
+        <v>4903.86</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SERVIÇO DE LICENÇA DO SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteúdo web.</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025NE0001472</t>
+          <t>2025NE0001473</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5704.84</v>
+        <v>364.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2528,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025NE0001473</t>
+          <t>2025NE0001472</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>364.9</v>
+        <v>5704.84</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
@@ -2588,17 +2588,21 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024NE0001112</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>2024NE0001113</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>643/2022</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>20/08/2024</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2618.42</v>
+        <v>2715.04</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2614,21 +2618,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024NE0001113</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>643/2022</t>
-        </is>
-      </c>
+          <t>2024NE0001112</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>20/08/2024</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2715.04</v>
+        <v>2618.42</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2644,12 +2644,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2018NE00185</t>
+          <t>2018NE00189</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12862.8</v>
+        <v>10381.15</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2667,19 +2667,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE ACESSO GERENCIADO À REDE MUNDIAL, VIA REDE DE GOVERNO, ESTABELECENDO COMUNICAÇÃO A PARTIR DE CIRCUITO DE DADOS.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER OS CADASTROS DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2018NE00184</t>
+          <t>2018NE00167</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16228.19</v>
+        <v>3596.08</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2697,14 +2697,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEUDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VIDEOS E IMAGENS VIA WEBSITE.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL CTBG.ads</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2018NE00183</t>
+          <t>2018NE00173</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2734,17 +2734,21 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2018NE00182</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>2018NE00168</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>351/2017</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>20/03/2018</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10381.15</v>
+        <v>11300.02</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2753,7 +2757,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE NOTA DE EMPENHO POR EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb).</t>
         </is>
       </c>
     </row>
@@ -2786,21 +2790,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2018NE00168</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>351/2017</t>
-        </is>
-      </c>
+          <t>2018NE00182</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>20/03/2018</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11300.02</v>
+        <v>10381.15</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2809,14 +2809,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb).</t>
+          <t>ANULAÇÃO DE NOTA DE EMPENHO POR EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2018NE00173</t>
+          <t>2018NE00183</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2846,12 +2846,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2018NE00167</t>
+          <t>2018NE00184</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3596.08</v>
+        <v>16228.19</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2869,19 +2869,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL CTBG.ads</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEUDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VIDEOS E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2018NE00189</t>
+          <t>2018NE00185</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10381.15</v>
+        <v>12862.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2899,21 +2899,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER OS CADASTROS DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE ACESSO GERENCIADO À REDE MUNDIAL, VIA REDE DE GOVERNO, ESTABELECENDO COMUNICAÇÃO A PARTIR DE CIRCUITO DE DADOS.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2023NE00616</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>425/2021</t>
-        </is>
-      </c>
+          <t>2023NE0000616</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>19/05/2023</t>
@@ -2929,17 +2925,21 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1º Termo de Aditamento ao Contrato 425/2021 de Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 425/20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2023NE0000616</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>2023NE00616</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>425/2021</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>19/05/2023</t>
@@ -2955,19 +2955,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 425/20</t>
+          <t>1º Termo de Aditamento ao Contrato 425/2021 de Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024NE0001212</t>
+          <t>2024NE0001210</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1991.54</v>
+        <v>2715.04</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024NE0001210</t>
+          <t>2024NE0001212</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2715.04</v>
+        <v>1991.54</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2023NE0000986</t>
+          <t>2023NE0000984</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2618.42</v>
+        <v>3983.08</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 427/2021 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2023NE0000984</t>
+          <t>2023NE0000986</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3983.08</v>
+        <v>2618.42</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3123,19 +3123,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 427/2021 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2017NE00586</t>
+          <t>2017NE00578</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>449.51</v>
+        <v>6777.44</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3153,19 +3153,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 14741 - DATADA 10/06/2015, RD Nº 2016RD00192</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2017NE00577</t>
+          <t>2017NE00585</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6777.44</v>
+        <v>449.51</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3183,19 +3183,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 15108 - DATADA 10/07/2015, RD Nº 2016RD00209</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2017NE00597</t>
+          <t>2017NE00584</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6777.44</v>
+        <v>284.69</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3213,19 +3213,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 15680 - DATADA 10/09/2015, RD Nº 2016RD00147</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2017NE00599</t>
+          <t>2017NE00591</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6777.44</v>
+        <v>720.11</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17019 - DATADA 16/12/2015, RD Nº 2016RD00203</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2017NE00580</t>
+          <t>2017NE00598</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>449.51</v>
+        <v>6777.44</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3273,19 +3273,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 17022 - DATADA 16/12/2015, RD Nº 2016RD00200</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2017NE00579</t>
+          <t>2017NE00592</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6777.44</v>
+        <v>742.79</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3303,19 +3303,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17016 - DATADA 16/12/2015, RD Nº 2016RD00201</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2017NE00583</t>
+          <t>2017NE00590</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>449.51</v>
+        <v>742.79</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3333,19 +3333,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 15385 - DATADA 25/08/2015, RD Nº 2016RD00196</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17020 - DATADA 16/12/2015, RD Nº 2016RD00204</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2017NE00594</t>
+          <t>2017NE00588</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6777.44</v>
+        <v>1445.26</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3363,19 +3363,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17075 - DATADA 23/12/2015, RD Nº 2016RD00205</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2017NE00596</t>
+          <t>2017NE00581</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6777.44</v>
+        <v>449.51</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3393,19 +3393,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 17018 - DATADA 16/12/2015, RD Nº 2016RD00198</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2017NE00582</t>
+          <t>2017NE00595</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>164.82</v>
+        <v>6777.44</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 17017 - DATADA 16/12/2015, RD Nº 2016RD00197</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2017NE00595</t>
+          <t>2017NE00582</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6777.44</v>
+        <v>164.82</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3483,19 +3483,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 17017 - DATADA 16/12/2015, RD Nº 2016RD00197</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2017NE00581</t>
+          <t>2017NE00596</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>449.51</v>
+        <v>6777.44</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3513,19 +3513,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 17018 - DATADA 16/12/2015, RD Nº 2016RD00198</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2017NE00588</t>
+          <t>2017NE00594</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1445.26</v>
+        <v>6777.44</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3543,19 +3543,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17075 - DATADA 23/12/2015, RD Nº 2016RD00205</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2017NE00590</t>
+          <t>2017NE00583</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>742.79</v>
+        <v>449.51</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17020 - DATADA 16/12/2015, RD Nº 2016RD00204</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 15385 - DATADA 25/08/2015, RD Nº 2016RD00196</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2017NE00592</t>
+          <t>2017NE00579</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>742.79</v>
+        <v>6777.44</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3603,19 +3603,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17016 - DATADA 16/12/2015, RD Nº 2016RD00201</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2017NE00598</t>
+          <t>2017NE00580</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6777.44</v>
+        <v>449.51</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 17022 - DATADA 16/12/2015, RD Nº 2016RD00200</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2017NE00591</t>
+          <t>2017NE00599</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>720.11</v>
+        <v>6777.44</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3663,19 +3663,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL NFS-e Nº 17019 - DATADA 16/12/2015, RD Nº 2016RD00203</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2017NE00584</t>
+          <t>2017NE00597</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>284.69</v>
+        <v>6777.44</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3693,19 +3693,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 15680 - DATADA 10/09/2015, RD Nº 2016RD00147</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2017NE00585</t>
+          <t>2017NE00577</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>449.51</v>
+        <v>6777.44</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3723,19 +3723,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 15108 - DATADA 10/07/2015, RD Nº 2016RD00209</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2017NE00578</t>
+          <t>2017NE00586</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6777.44</v>
+        <v>449.51</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL (CTBG). NFS-e Nº 14741 - DATADA 10/06/2015, RD Nº 2016RD00192</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024NE0001267</t>
+          <t>2024NE0001268</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>178.09</v>
+        <v>1991.54</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3813,19 +3813,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024NE0001268</t>
+          <t>2024NE0001267</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1991.54</v>
+        <v>178.09</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3843,21 +3843,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2023NE00571</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>427/2021</t>
-        </is>
-      </c>
+          <t>2023NE0000571</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
           <t>16/05/2023</t>
@@ -3873,21 +3869,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1º Termo Aditamento ao Contrato 427/2021 - Prestação de Serviços PRODAM-RH.</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 427/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2023NE00570</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>643/2022</t>
-        </is>
-      </c>
+          <t>2023NE0000570</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
           <t>16/05/2023</t>
@@ -3903,17 +3895,21 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Contrato 643/2022 de Prestação de Serviços de Conteúdo Web e Licença de uso de sistema de informação,</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2023NE0000570</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>2023NE00570</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>643/2022</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>16/05/2023</t>
@@ -3929,17 +3925,21 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Contrato 643/2022 de Prestação de Serviços de Conteúdo Web e Licença de uso de sistema de informação,</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2023NE0000571</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>2023NE00571</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>427/2021</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>16/05/2023</t>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 427/2021 AD: 01.</t>
+          <t>1º Termo Aditamento ao Contrato 427/2021 - Prestação de Serviços PRODAM-RH.</t>
         </is>
       </c>
     </row>
@@ -4052,21 +4052,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2017NE00630</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>P.98/2016</t>
-        </is>
-      </c>
+          <t>2017NE00574</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6602.34</v>
+        <v>449.51</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4075,14 +4071,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2017NE00639</t>
+          <t>2017NE00638</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4096,7 +4092,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1950.54</v>
+        <v>694.28</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4112,12 +4108,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2017NE00632</t>
+          <t>2017NE00637</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>P.178/2015</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4126,7 +4122,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6777.44</v>
+        <v>568.28</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4135,19 +4131,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL E COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA </t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS CFPP CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2017NE00634</t>
+          <t>2017NE00636</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4156,7 +4152,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>449.51</v>
+        <v>1118.81</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4165,19 +4161,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS CFPP CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2017NE00633</t>
+          <t>2017NE00635</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>P.98/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4186,7 +4182,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6602.34</v>
+        <v>449.51</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4195,19 +4191,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS DE TELECOMUNICAÇÃO, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWAL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA P</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2017NE00626</t>
+          <t>2017NE00631</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.98/2016</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4216,7 +4212,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>449.51</v>
+        <v>6602.34</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4225,28 +4221,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2017NE00624</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>294/2016</t>
-        </is>
-      </c>
+          <t>2017NE00575</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>617.42</v>
+        <v>449.51</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4255,28 +4247,24 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTOS DO SISTEMA CFPP CADASTRO DE FOLHA DE PEGAMENTO DE PESSOAL</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2017NE00628</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>295/2016</t>
-        </is>
-      </c>
+          <t>2017NE00576</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>449.51</v>
+        <v>6602.34</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4285,14 +4273,14 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2017NE00629</t>
+          <t>2017NE00565</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4315,19 +4303,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20227 DATADA 06/10/2016, CONFORME RD Nº 2017RD00017</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2017NE00623</t>
+          <t>2017NE00570</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4336,7 +4324,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>643.25</v>
+        <v>449.51</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4345,21 +4333,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTOS DO SISTEMA CFPP CADASTRO DE FOLHA DE PEGAMENTO DE PESSOAL</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20226 DATADA 06/10/2016, CONFORME RD Nº 2017RD00016</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2017NE00627</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>295/2016</t>
-        </is>
-      </c>
+          <t>2017NE00572</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>14/07/2017</t>
@@ -4375,14 +4359,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2017NE00564</t>
+          <t>2017NE00563</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4405,24 +4389,28 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20225 DATADA 06/10/2016, CONFORME RD Nº 2017RD00015</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20224 DATADA 06/10/2016, CONFORME RD Nº 2017RD00018</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2017NE00573</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>2017NE00562</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>P.98/2016</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>449.51</v>
+        <v>6602.34</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4431,7 +4419,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
@@ -4468,21 +4456,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2017NE00562</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>P.98/2016</t>
-        </is>
-      </c>
+          <t>2017NE00573</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6602.34</v>
+        <v>449.51</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4491,14 +4475,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2017NE00563</t>
+          <t>2017NE00564</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4521,17 +4505,21 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20224 DATADA 06/10/2016, CONFORME RD Nº 2017RD00018</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20225 DATADA 06/10/2016, CONFORME RD Nº 2017RD00015</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2017NE00572</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>2017NE00627</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>295/2016</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
           <t>14/07/2017</t>
@@ -4547,19 +4535,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2017NE00570</t>
+          <t>2017NE00623</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4568,7 +4556,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>449.51</v>
+        <v>643.25</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4577,14 +4565,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20226 DATADA 06/10/2016, CONFORME RD Nº 2017RD00016</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTOS DO SISTEMA CFPP CADASTRO DE FOLHA DE PEGAMENTO DE PESSOAL</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2017NE00565</t>
+          <t>2017NE00629</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4607,24 +4595,28 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG. NFS-e Nº 20227 DATADA 06/10/2016, CONFORME RD Nº 2017RD00017</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2017NE00576</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>2017NE00628</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>295/2016</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6602.34</v>
+        <v>449.51</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4633,24 +4625,28 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2017NE00575</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>2017NE00624</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>294/2016</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>449.51</v>
+        <v>617.42</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4659,19 +4655,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTOS DO SISTEMA CFPP CADASTRO DE FOLHA DE PEGAMENTO DE PESSOAL</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2017NE00631</t>
+          <t>2017NE00626</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>P.98/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4680,7 +4676,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6602.34</v>
+        <v>449.51</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4689,19 +4685,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2017NE00635</t>
+          <t>2017NE00633</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>P.98/2016</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4710,7 +4706,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>449.51</v>
+        <v>6602.34</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4719,19 +4715,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS DE TELECOMUNICAÇÃO, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWAL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA P</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2017NE00636</t>
+          <t>2017NE00634</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4740,7 +4736,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1118.81</v>
+        <v>449.51</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4749,19 +4745,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS CFPP CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE SISTEMA DE CONTABILIDADE GERENCIAL - CTBG</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2017NE00637</t>
+          <t>2017NE00632</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>P.178/2015</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4770,7 +4766,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>568.28</v>
+        <v>6777.44</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4779,14 +4775,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS CFPP CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL.</t>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL E COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA </t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2017NE00638</t>
+          <t>2017NE00639</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4800,7 +4796,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>694.28</v>
+        <v>1950.54</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4816,17 +4812,21 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2017NE00574</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>2017NE00630</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>P.98/2016</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
           <t>14/07/2017</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>449.51</v>
+        <v>6602.34</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4835,19 +4835,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO POR EQUIVOCO NA FONTE DO RECURSO.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO A DISPONIBILIDADE DE CANAL DE COMUNICAÇÃO VIA FIBRA ÓPTICA, FIREWALL UTM PARA ACESSAR AOS SISTEMAS RESIDENTES NO COMPUTADOR CENTRAL DA</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2022NE0001327</t>
+          <t>2022NE0001328</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>321.76</v>
+        <v>3668</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4865,19 +4865,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>reforço da NE 41/2022</t>
+          <t>REFORÇO DA NE 52/2022</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2022NE0001328</t>
+          <t>2022NE0001327</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3668</v>
+        <v>321.76</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 52/2022</t>
+          <t>reforço da NE 41/2022</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4932,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021NE0000900</t>
+          <t>2021NE0000901</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6375.8</v>
+        <v>5683.84</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4955,19 +4955,19 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>reforço da ne 16/2021</t>
+          <t>reforço da ne 15/2021</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021NE0000901</t>
+          <t>2021NE0000900</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>5683.84</v>
+        <v>6375.8</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4985,19 +4985,19 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>reforço da ne 15/2021</t>
+          <t>reforço da ne 16/2021</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021NE0001719</t>
+          <t>2021NE0001724</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6940.36</v>
+        <v>3836.61</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5015,19 +5015,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>REFORÇO DA ne 35/2021</t>
+          <t>reforço da NE 15/2021</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021NE0001724</t>
+          <t>2021NE0001719</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3836.61</v>
+        <v>6940.36</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5045,14 +5045,14 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>reforço da NE 15/2021</t>
+          <t>REFORÇO DA ne 35/2021</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2020NE02639</t>
+          <t>2020NE02638</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2125.26</v>
+        <v>1733.88</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Anulação Orçamentária parcial da NE nº 08/2020, em atendimento ao Decreto nº 42.146 de 31 de março de 2020 que dispõe sobre o plano de contingenciamento de gastos, no âmbito do poder executivo estadua</t>
+          <t>Anulação Orçamentária parcial da NE nº 06/2020, em atendimento ao Decreto nº 42.146 de 31 de março de 2020 que dispõe sobre o plano de contingenciamento de gastos, no âmbito do poder executivo estadua</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020NE02638</t>
+          <t>2020NE02639</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1733.88</v>
+        <v>2125.26</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5123,19 +5123,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Anulação Orçamentária parcial da NE nº 06/2020, em atendimento ao Decreto nº 42.146 de 31 de março de 2020 que dispõe sobre o plano de contingenciamento de gastos, no âmbito do poder executivo estadua</t>
+          <t>Anulação Orçamentária parcial da NE nº 08/2020, em atendimento ao Decreto nº 42.146 de 31 de março de 2020 que dispõe sobre o plano de contingenciamento de gastos, no âmbito do poder executivo estadua</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2024NE0000981</t>
+          <t>2024NE0000978</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3983.08</v>
+        <v>356.18</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5153,19 +5153,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2024NE0000978</t>
+          <t>2024NE0000981</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>356.18</v>
+        <v>3983.08</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2024NE0000739</t>
+          <t>2024NE0000737</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3983.08</v>
+        <v>356.18</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5310,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2024NE0000737</t>
+          <t>2024NE0000739</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>356.18</v>
+        <v>3983.08</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024NE0000091</t>
+          <t>2024NE0000090</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>178.09</v>
+        <v>2618.42</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
@@ -5520,12 +5520,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2024NE0000090</t>
+          <t>2024NE0000091</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2618.42</v>
+        <v>178.09</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
@@ -5580,10 +5580,14 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2024NE0001428</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr"/>
+          <t>2024NE0001445</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>427/2021</t>
+        </is>
+      </c>
       <c r="C172" t="inlineStr">
         <is>
           <t>07/11/2024</t>
@@ -5599,24 +5603,28 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>anulação de Empenho.</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2024NE0001427</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
+          <t>2024NE0001442</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>425/2021</t>
+        </is>
+      </c>
       <c r="C173" t="inlineStr">
         <is>
           <t>07/11/2024</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>182.45</v>
+        <v>364.9</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5625,7 +5633,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ajustes da célula Orçamentaria</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
@@ -5662,21 +5670,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2024NE0001442</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>425/2021</t>
-        </is>
-      </c>
+          <t>2024NE0001427</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>07/11/2024</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>364.9</v>
+        <v>182.45</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5685,21 +5689,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>ajustes da célula Orçamentaria</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2024NE0001445</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>427/2021</t>
-        </is>
-      </c>
+          <t>2024NE0001428</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
           <t>07/11/2024</t>
@@ -5715,14 +5715,14 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
+          <t>anulação de Empenho.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2015NE00137</t>
+          <t>2015NE00140</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>449.51</v>
+        <v>587.61</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5741,14 +5741,14 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 107/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA DE CONTABILIDADE GERENCIAL (CBTG), N.F.S.-e Nº 12</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 111/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA CAD/FOLHA DE PAGAMENTO DE PESSOAL - CFPP, N.F.S.-</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2015NE00139</t>
+          <t>2015NE00141</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -5767,14 +5767,14 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 112/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA CAD/FOLHA DE PAGAMENTO DE PESSOAL - CFPP, N.F.S.-</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 110/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA CAD/FOLHA DE PAGAMENTO DE PESSOAL - CFPP, N.F.S.-</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2015NE00138</t>
+          <t>2015NE00127</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>449.51</v>
+        <v>8871.389999999999</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 106/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA DE CONTABILIDADE GERENCIAL (CBTG), N.F.S.-e Nº 12</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCICIOS ANTERIORES Nº 108/2015, PRESTAÇÃO DE SERVIÇOS DE DE LINK DE INTERNET, CONFORME N.F.S-e Nº 12686 E 12687, EMITIDAS EM 03/12/2014.</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2015NE00127</t>
+          <t>2015NE00138</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>8871.389999999999</v>
+        <v>449.51</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5845,14 +5845,14 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCICIOS ANTERIORES Nº 108/2015, PRESTAÇÃO DE SERVIÇOS DE DE LINK DE INTERNET, CONFORME N.F.S-e Nº 12686 E 12687, EMITIDAS EM 03/12/2014.</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 106/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA DE CONTABILIDADE GERENCIAL (CBTG), N.F.S.-e Nº 12</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2015NE00141</t>
+          <t>2015NE00139</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 110/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA CAD/FOLHA DE PAGAMENTO DE PESSOAL - CFPP, N.F.S.-</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 112/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA CAD/FOLHA DE PAGAMENTO DE PESSOAL - CFPP, N.F.S.-</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2015NE00140</t>
+          <t>2015NE00137</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>587.61</v>
+        <v>449.51</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 111/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA CAD/FOLHA DE PAGAMENTO DE PESSOAL - CFPP, N.F.S.-</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE DESPESAS DE EXECICIOS ANTERIORES Nº 107/2015, PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS SISTEMA DE CONTABILIDADE GERENCIAL (CBTG), N.F.S.-e Nº 12</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2022NE0000276</t>
+          <t>2022NE0000277</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>643.52</v>
+        <v>7336</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5987,19 +5987,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>reforço da ne 41/22</t>
+          <t>reforço da ne 52/22</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2022NE0000277</t>
+          <t>2022NE0000276</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7336</v>
+        <v>643.52</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6017,19 +6017,19 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>reforço da ne 52/22</t>
+          <t>reforço da ne 41/22</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026NE0000016</t>
+          <t>2026NE0000015</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1952.6</v>
+        <v>21288.2</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6047,19 +6047,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026NE0000015</t>
+          <t>2026NE0000016</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>21288.2</v>
+        <v>1952.6</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6077,19 +6077,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 04.</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2015NE00053</t>
+          <t>2015NE00007</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>102/2012</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1348.53</v>
+        <v>26614.21</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6107,19 +6107,19 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>REFERENTE AO 2º TERMO ADITIVO COM O OBJETO DE PRORROGAR POR MAIS DOZE MESES, COM REAJUSTE DE 5,52%, CONFORME IGPM ACUMULADO NO PERÍODO DE VIGÊNCIA E SEGUNDO A CLAUSULA DECIMA PRIMEIRA DO CONTRATO ORIG</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2015NE00034</t>
+          <t>2015NE00022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>102/2012</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>26614.21</v>
+        <v>1348.53</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6137,19 +6137,19 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>ANULAÇÃO DE N.E. Nº 2015NE00009, POR EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2015NE00036</t>
+          <t>2015NE00011</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>274/2010</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1348.53</v>
+        <v>1762.83</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6167,19 +6167,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 428/2013. OBJETO: PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE CONTABILIDADE GERENCIAL ¿ CTBG. OBJETIVO: PRORROGAR POR MAIS 12 (DOZE) MESES, COM READEQUAÇÃO FIN</t>
+          <t>REFERENTE AO 4º TERMO ADITIVO PARA PRORROGAÇÃO POR MAIS 12 (DOZE) MESES, COM READEQUAÇÃO FINANCEIRA, O TERMO DE CONTRATO Nº 274/2010, DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADAST</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2015NE00020</t>
+          <t>2015NE00009</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>102/2012</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>26614.21</v>
+        <v>1348.53</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6197,19 +6197,19 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE N.E. Nº 2015NE00007, POR EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>REFERENTE AO 1º TERMO ADITIVO PARA PRORROGAR POR MAIS 12 (DOZE) MESES O CONTRATO Nº 428/2013, OBJETO: PRESTAÇÃO DE SERVIÇOS DESISTEMA DE CONTABILIDADE GERENCIAL (CTBG), COM READEQUAÇÃO FINANCEIRA.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2015NE00051</t>
+          <t>2015NE00024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>274/2010</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1348.53</v>
+        <v>1762.83</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE NE Nº 2015NE00036, POR EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>ANULAÇÃO DE N.E. Nº 2015NE00011, POR EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6264,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2015NE00024</t>
+          <t>2015NE00051</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>274/2010</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1762.83</v>
+        <v>1348.53</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6287,19 +6287,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE N.E. Nº 2015NE00011, POR EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>ANULAÇÃO DE NE Nº 2015NE00036, POR EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2015NE00009</t>
+          <t>2015NE00020</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>102/2012</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1348.53</v>
+        <v>26614.21</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6317,19 +6317,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>REFERENTE AO 1º TERMO ADITIVO PARA PRORROGAR POR MAIS 12 (DOZE) MESES O CONTRATO Nº 428/2013, OBJETO: PRESTAÇÃO DE SERVIÇOS DESISTEMA DE CONTABILIDADE GERENCIAL (CTBG), COM READEQUAÇÃO FINANCEIRA.</t>
+          <t>ANULAÇÃO DE N.E. Nº 2015NE00007, POR EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2015NE00011</t>
+          <t>2015NE00036</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>274/2010</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1762.83</v>
+        <v>1348.53</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6347,19 +6347,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>REFERENTE AO 4º TERMO ADITIVO PARA PRORROGAÇÃO POR MAIS 12 (DOZE) MESES, COM READEQUAÇÃO FINANCEIRA, O TERMO DE CONTRATO Nº 274/2010, DE PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP - CADAST</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 428/2013. OBJETO: PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE CONTABILIDADE GERENCIAL ¿ CTBG. OBJETIVO: PRORROGAR POR MAIS 12 (DOZE) MESES, COM READEQUAÇÃO FIN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2015NE00022</t>
+          <t>2015NE00034</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>428/2013</t>
+          <t>102/2012</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1348.53</v>
+        <v>26614.21</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6377,19 +6377,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE N.E. Nº 2015NE00009, POR EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2015NE00007</t>
+          <t>2015NE00053</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>102/2012</t>
+          <t>428/2013</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>26614.21</v>
+        <v>1348.53</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6407,19 +6407,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>REFERENTE AO 2º TERMO ADITIVO COM O OBJETO DE PRORROGAR POR MAIS DOZE MESES, COM REAJUSTE DE 5,52%, CONFORME IGPM ACUMULADO NO PERÍODO DE VIGÊNCIA E SEGUNDO A CLAUSULA DECIMA PRIMEIRA DO CONTRATO ORIG</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021NE0000015</t>
+          <t>2021NE0000008</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5683.84</v>
+        <v>1749.04</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6437,19 +6437,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH; MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL; PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE PAGAMENT</t>
+          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteudo web.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021NE0000006</t>
+          <t>2021NE0000016</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6430.32</v>
+        <v>6375.8</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6467,19 +6467,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviços de acesso à rede mundial de computadores (internet), via rede de governo, estabelecendo comunicação a partir de circuito de dados, com velocidade de 1</t>
+          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021NE0000016</t>
+          <t>2021NE0000006</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>6375.8</v>
+        <v>6430.32</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6497,19 +6497,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS.</t>
+          <t>Contratação de empresa para prestação de serviços de acesso à rede mundial de computadores (internet), via rede de governo, estabelecendo comunicação a partir de circuito de dados, com velocidade de 1</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021NE0000008</t>
+          <t>2021NE0000015</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1749.04</v>
+        <v>5683.84</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteudo web.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH; MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL; PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE PAGAMENT</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6594,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2017NE00399</t>
+          <t>2017NE00398</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>4486</v>
+        <v>1798.04</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE FOLHA DE PAGAMENTO - CFPP.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL-CTBG.</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2017NE00398</t>
+          <t>2017NE00399</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1798.04</v>
+        <v>4486</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6677,19 +6677,19 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL-CTBG.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE FOLHA DE PAGAMENTO - CFPP.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025NE0000016</t>
+          <t>2025NE0000018</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>427/2021</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>5430.08</v>
+        <v>4135.24</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025NE0000018</t>
+          <t>2025NE0000016</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>427/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>4135.24</v>
+        <v>5430.08</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6767,19 +6767,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de processamento do Sistema CFPP, PRODAM RH; Manter cadastro dos servidores e folha de pagamento pessoal, entre outros, conforme TDR. TC: 0427/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2024NE0000029</t>
+          <t>2024NE0000030</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>425/2021</t>
+          <t>643/2022</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>356.18</v>
+        <v>5236.84</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6797,19 +6797,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
+          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2024NE0000030</t>
+          <t>2024NE0000029</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>643/2022</t>
+          <t>425/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>5236.84</v>
+        <v>356.18</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de conteúdo web e licença de uso de sistema de informação, com a disponibilização de Gestor de Conteúdo Web, constante no item 4 deste Ter</t>
+          <t>Prestação de serviços técnicos especializados em informática, compreendendo a disponibilização de clientes VPN (VIRTUAL PRIVATE NETWORK), para atender à necessidade desta ADS, conforme TDR. TC: 0425/2</t>
         </is>
       </c>
     </row>
@@ -6864,12 +6864,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2020NE00013</t>
+          <t>2020NE00006</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1634.62</v>
+        <v>15460.43</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6887,19 +6887,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteúdo web.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH; MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL; PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE PAGAMENT</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2020NE00008</t>
+          <t>2020NE00007</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>14168.4</v>
+        <v>6430.32</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6917,19 +6917,19 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS.</t>
+          <t>Serviço de acesso gerencial a rede mundial via rede de governo (link de internet).</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2020NE00007</t>
+          <t>2020NE00008</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6430.32</v>
+        <v>14168.4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6947,19 +6947,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Serviço de acesso gerencial a rede mundial via rede de governo (link de internet).</t>
+          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2020NE00006</t>
+          <t>2020NE00013</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>15460.43</v>
+        <v>1634.62</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6977,14 +6977,14 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH; MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL; PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS PARA EFETIVAÇÃO DE PAGAMENT</t>
+          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteúdo web.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2019NE00026</t>
+          <t>2019NE00043</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7014,21 +7014,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2019NE00029</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00042</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1475.29</v>
+        <v>1484.04</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7037,19 +7033,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE TIC COMPREENDENDO A LICENÇA DE USO DO GESTOR DE CONTEÚDO WEB.</t>
+          <t>Correção na descrição.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2019NE00024</t>
+          <t>2019NE00027</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7058,7 +7054,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>5313.15</v>
+        <v>4334.7</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7067,7 +7063,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL.</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7100,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2019NE00027</t>
+          <t>2019NE00024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7118,7 +7114,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>4334.7</v>
+        <v>5313.15</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7127,24 +7123,28 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL.</t>
+          <t>Prestação de serviço de execução de sistema de protocolo em plataforma WEB (SPROWEB), para o controle de acompanhamento de registro de todos os documentos ou processos da ADS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2019NE00042</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr"/>
+          <t>2019NE00029</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C225" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1484.04</v>
+        <v>1475.29</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7153,14 +7153,14 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Correção na descrição.</t>
+          <t>SERVIÇOS DE TIC COMPREENDENDO A LICENÇA DE USO DO GESTOR DE CONTEÚDO WEB.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2019NE00043</t>
+          <t>2019NE00026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7190,12 +7190,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2018NE00017</t>
+          <t>2018NE00014</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>13248.92</v>
+        <v>11215</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7213,19 +7213,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb).</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER OS CADASTROS DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2018NE00016</t>
+          <t>2018NE00015</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1475.29</v>
+        <v>4495.1</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7243,19 +7243,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÃO, NOTÍCIAS, VÍDEOS E IMAGENS VIA WEBSITE.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL CTBG.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2018NE00015</t>
+          <t>2018NE00016</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>4495.1</v>
+        <v>1475.29</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7273,19 +7273,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL CTBG.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÃO, NOTÍCIAS, VÍDEOS E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2018NE00014</t>
+          <t>2018NE00017</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>11215</v>
+        <v>13248.92</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7303,19 +7303,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER OS CADASTROS DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELATÓRIOS.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb).</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2017NE00014</t>
+          <t>2017NE00015</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>4486</v>
+        <v>1798.04</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7333,19 +7333,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE FOLHA DE PAGAMENTO - CFPP.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL-CTBG.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2017NE00015</t>
+          <t>2017NE00014</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1798.04</v>
+        <v>4486</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7363,19 +7363,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL-CTBG.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE FOLHA DE PAGAMENTO - CFPP.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2014NE00041</t>
+          <t>2014NE00010</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>102/2012</t>
+          <t>274/2010</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>25221.93</v>
+        <v>4776.87</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7393,19 +7393,19 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Contrato No. 102/2012 - Ponto-a-ponto 3Mb, Internet 2Mb, Locação Equipamento Firewall</t>
+          <t>Contrato No. 274/2010 - CFPP - Cadastro e Folha de Pagamento de Pessoal</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2014NE00010</t>
+          <t>2014NE00041</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>274/2010</t>
+          <t>102/2012</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>4776.87</v>
+        <v>25221.93</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7423,19 +7423,19 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Contrato No. 274/2010 - CFPP - Cadastro e Folha de Pagamento de Pessoal</t>
+          <t>Contrato No. 102/2012 - Ponto-a-ponto 3Mb, Internet 2Mb, Locação Equipamento Firewall</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2017NE01181</t>
+          <t>2017NE01184</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1656.12</v>
+        <v>1475.29</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7453,19 +7453,19 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb). OBJETIVO: CONTROLE E ACOMPANHAMENTO DO REGISTRO DE TODOS OS DOCUMENTOS OU PROCESSOS DESTA ADS.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEUDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VIDEOS E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2017NE01184</t>
+          <t>2017NE01181</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1475.29</v>
+        <v>1656.12</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7483,19 +7483,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEUDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VIDEOS E IMAGENS VIA WEBSITE.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb). OBJETIVO: CONTROLE E ACOMPANHAMENTO DO REGISTRO DE TODOS OS DOCUMENTOS OU PROCESSOS DESTA ADS.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2019NE01380</t>
+          <t>2019NE01379</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>19290.96</v>
+        <v>5313.15</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7513,19 +7513,19 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>reforço da NE 65/2019</t>
+          <t>REFORÇO DA NE 1110/2019</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2019NE01381</t>
+          <t>2019NE01383</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>4903.86</v>
+        <v>840.96</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 66/2019</t>
+          <t>REFORÇO DA NE 43/2019</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2019NE01383</t>
+          <t>2019NE01381</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>840.96</v>
+        <v>4903.86</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7603,19 +7603,19 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 43/2019</t>
+          <t>REFORÇO DA NE 66/2019</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2019NE01379</t>
+          <t>2019NE01380</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>5313.15</v>
+        <v>19290.96</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7633,19 +7633,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 1110/2019</t>
+          <t>reforço da NE 65/2019</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2017NE00921</t>
+          <t>2017NE01011</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>351/2017</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>3312.24</v>
+        <v>2950.58</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7663,19 +7663,19 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb). OBJETIVO: CONTROLE E ACOMPANHAMENTO DO REGISTRO DE TODOS OS DOCUMENTOS OU PROCESSOS DESTA ADS.</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEUDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VIDEOS E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2017NE01023</t>
+          <t>2017NE01022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>294/2016</t>
+          <t>295/2016</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2243.01</v>
+        <v>899.02</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7693,19 +7693,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE FOLHA DE PAGAMENTO - CFPP.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL-CTBG.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2017NE01022</t>
+          <t>2017NE01023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>295/2016</t>
+          <t>294/2016</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>899.02</v>
+        <v>2243.01</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7723,19 +7723,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE CONTABILIDADE GERENCIAL-CTBG.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE SISTEMA DE FOLHA DE PAGAMENTO - CFPP.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2017NE01011</t>
+          <t>2017NE00921</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>351/2017</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>2950.58</v>
+        <v>3312.24</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7753,28 +7753,24 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEUDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VIDEOS E IMAGENS VIA WEBSITE.</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb). OBJETIVO: CONTROLE E ACOMPANHAMENTO DO REGISTRO DE TODOS OS DOCUMENTOS OU PROCESSOS DESTA ADS.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2019NE00937</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2/2018</t>
-        </is>
-      </c>
+          <t>2019NE00936</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>19290.96</v>
+        <v>4903.86</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7783,28 +7779,24 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>link de internet</t>
+          <t>serv. de licença de uso de sistema de informação</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2019NE00938</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>351/2017</t>
-        </is>
-      </c>
+          <t>2019NE00939</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3542.1</v>
+        <v>4334.7</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7813,7 +7805,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>sproweb</t>
+          <t>folha de pagamento</t>
         </is>
       </c>
     </row>
@@ -7846,17 +7838,21 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2019NE00939</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>2019NE00938</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>351/2017</t>
+        </is>
+      </c>
       <c r="C249" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>4334.7</v>
+        <v>3542.1</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7865,24 +7861,28 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>folha de pagamento</t>
+          <t>sproweb</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2019NE00936</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>2019NE00937</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2/2018</t>
+        </is>
+      </c>
       <c r="C250" t="inlineStr">
         <is>
           <t>01/07/2019</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>4903.86</v>
+        <v>19290.96</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7891,14 +7891,14 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>serv. de licença de uso de sistema de informação</t>
+          <t>link de internet</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2018NE00049</t>
+          <t>2018NE00052</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>3596.08</v>
+        <v>12862.8</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2018NE00051</t>
+          <t>2018NE00048</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>16228.19</v>
+        <v>11300.02</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2018NE00048</t>
+          <t>2018NE00051</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>11300.02</v>
+        <v>16228.19</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2018NE00052</t>
+          <t>2018NE00049</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>12862.8</v>
+        <v>3596.08</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8028,12 +8028,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2019NE00065</t>
+          <t>2019NE00066</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>12860.64</v>
+        <v>3269.24</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8051,19 +8051,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Serviço de acesso gerencial a rede mundial via rede de governo (link de internet).</t>
+          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteúdo web.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2019NE00066</t>
+          <t>2019NE00065</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>3269.24</v>
+        <v>12860.64</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Serviço de TIC compreendendo a licença de uso do gestor de conteúdo web.</t>
+          <t>Serviço de acesso gerencial a rede mundial via rede de governo (link de internet).</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/ADS/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/ADS/dossie.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2030-11-30</t>
         </is>
       </c>
     </row>
